--- a/Annotation/annotation_outputs/annotation_group_3.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_3.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>taxonomy_label_correct</t>
+          <t>label_correctness</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">

--- a/Annotation/annotation_outputs/annotation_group_3.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_3.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -40,12 +48,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,21 +109,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +511,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>case_id</t>
@@ -524,7 +558,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="65" customHeight="1">
       <c r="A2" s="4" t="n">
         <v>5</v>
       </c>
@@ -557,40 +591,40 @@
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>What is the name of the football club that Oliver Kahn played for in the year 2001</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>FC Bayern Munich</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FC Bayern Munich|Germany men's national association football team</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00033.json</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
         <v>21</v>
       </c>
@@ -623,40 +657,40 @@
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Who directs the first season “somebody’s dead” in the tv series Big Little Lies</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Jean-Marc Vallée</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Andrea Arnold|Jean-Marc Vallée</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00136.json</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
         <v>36</v>
       </c>
@@ -689,40 +723,40 @@
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>What is the sports team played in 2012 to 2014 by Alessandro Del Piero</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sydney FC</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Juventus FC|Odisha FC|Sydney FC</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00114.json</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
         <v>57</v>
       </c>
@@ -755,40 +789,40 @@
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>who is the owner of the mandalay bay in vegas</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>MGM Resorts International</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Mandalay Resort Group|MGM Resorts International</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00520.json</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
         <v>73</v>
       </c>
@@ -821,40 +855,40 @@
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Who played the role of Jonas Kahnwald as teen in Dark?</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Louis Hofmann</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Andreas Pietschmann|Louis Hofmann</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00140.json</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
         <v>88</v>
       </c>
@@ -887,40 +921,40 @@
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>What prize was the author William Golding awarded with in the year 1983</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Nobel Prize in Literature</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>honorary doctor of the Sorbonne Nouvelle University|Nobel Prize in Literature</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00126.json</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
         <v>108</v>
       </c>
@@ -953,40 +987,40 @@
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>112</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>At which football club did Argentine footballer Diego Maradona score the most goals</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Argentinos Juniors</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Argentinos Juniors|116</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00170.json</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>120</v>
       </c>
@@ -1019,40 +1053,40 @@
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>128</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>What was the name of the football club Mikel Arteta represented in the year 2003</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Rangers F.C.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Spain national under-21 association football team|Rangers F.C.</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00066.json</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>133</v>
       </c>
@@ -1085,40 +1119,40 @@
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>What was the first movie David Callaham wrote the screenplay for</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Doom</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Doom|2005-10-20T00:00:00Z</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00275.json</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>148</v>
       </c>
@@ -1151,40 +1185,40 @@
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="6" t="n">
         <v>156</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>What was the first movie that Mila Kunis who played Jackie on That '70s Show act in</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Santa with Muscles</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Santa with Muscles|1996-01-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00038.json</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>161</v>
       </c>
@@ -1217,40 +1251,40 @@
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="6" t="n">
         <v>168</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>What is the name of the first book of the series The Farseer Trilogy</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Assassin's Apprentice</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Assassin's Apprentice|1995-04-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00093.json</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>173</v>
       </c>
@@ -1283,40 +1317,40 @@
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="25" ht="65" customHeight="1">
+      <c r="A25" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Which movie has the longest run time in the Bridget Jones film series</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Bridget Jones's Baby</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Bridget Jones's Baby|122.0</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00141.json</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>185</v>
       </c>
@@ -1349,40 +1383,40 @@
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Which TV series with actor Charlie Sheen was created by Chuck Lorre</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Two and a Half Men</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Bookie|Two and a Half Men|The Big Bang Theory</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00292.json</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>196</v>
       </c>
@@ -1415,40 +1449,40 @@
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>What movie has a longer runtime, Hamlet or Gone With the Wind</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Hamlet</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Hamlet|150.0|Gone with the Wind|238.0</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00254.json</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
         <v>217</v>
       </c>
@@ -1481,40 +1515,40 @@
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="6" t="n">
         <v>229</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>what is the notable work by the Composer Tan Dun?</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>The First Emperor</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>The First Emperor|Marco Polo|Martial Arts Trilogy</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00027.json</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
         <v>237</v>
       </c>
@@ -1547,40 +1581,40 @@
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>when did the movie princess bride come out</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>September 25, 1987</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>1987-09-25T00:00:00Z|1988-10-13T00:00:00Z</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00893.json</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-    </row>
-    <row r="34">
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
         <v>265</v>
       </c>
@@ -1613,40 +1647,40 @@
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
+    <row r="35" ht="65" customHeight="1">
+      <c r="A35" s="6" t="n">
         <v>281</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Director's name for the initial four "Scream" movies?</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Wes Craven</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Wes Craven|Tyler Gillett|Matt Bettinelli-Olpin|Kevin Williamson</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00034.json</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
         <v>289</v>
       </c>
@@ -1679,40 +1713,40 @@
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
+    <row r="37" ht="65" customHeight="1">
+      <c r="A37" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>After their 2018 FIFA World Cup win how many wins did France national football team have</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00033.json</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-    </row>
-    <row r="38">
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
         <v>11</v>
       </c>
@@ -1745,40 +1779,40 @@
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+    <row r="39" ht="65" customHeight="1">
+      <c r="A39" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>As of 2020 how many gold medals has the United States women's national soccer team won</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00039.json</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-    </row>
-    <row r="40">
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
         <v>23</v>
       </c>
@@ -1820,40 +1854,40 @@
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+    <row r="41" ht="65" customHeight="1">
+      <c r="A41" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>What actress played Fiona "Fi" Phillips in So Weird?</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>Cara DeLizia</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Alexz Johnson</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00279.json</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
         <v>39</v>
       </c>
@@ -1895,40 +1929,40 @@
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="6" t="n">
         <v>46</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>How many Golden Globe Awards did One Flew Over the Cuckoo's Nest get</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00139.json</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
         <v>51</v>
       </c>
@@ -1961,40 +1995,40 @@
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
+    <row r="45" ht="65" customHeight="1">
+      <c r="A45" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>How many World Cup titles the Italy national football team has before winning it again in 2006</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00043.json</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
         <v>63</v>
       </c>
@@ -2036,21 +2070,21 @@
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>What are the named spirals ?</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>Archimedean spiral | Euler spiral | [[Fermats spiral]] (also parabolic spiral) | [[Cotess spiral]] | [[Poinsots spirals]]</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>Tadpole Galaxy|Tadpole Galaxy (lang:en)
 Triangulum Galaxy|Triangulum Galaxy (lang:en)
@@ -2063,21 +2097,21 @@
 Sombrero Galaxy|Sombrero Galaxy (lang:en)</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00057.json</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
         <v>79</v>
       </c>
@@ -2116,42 +2150,42 @@
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>What awards are national quality award ?</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Canada Awards for Excellence | Deming Prize | EFQM Excellence Award | Malcolm Baldrige National Quality Award | Philippine Quality Award | Rajiv Gandhi National Quality Award | Singapore Business Excellence Awards | Thailand Quality Award</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Rajiv Gandhi National Quality Award|Rajiv Gandhi National Quality Award (lang:en)
 Malcolm Baldrige National Quality Award|Malcolm Baldrige National Quality Award (lang:en)
 Viet Nam National Quality Award|Viet Nam National Quality Award (lang:en)</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00010.json</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50">
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
         <v>94</v>
       </c>
@@ -2184,40 +2218,40 @@
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="51" ht="65" customHeight="1">
+      <c r="A51" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>What is Luis Suárez National Team?</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>Uruguay Olympic football team, Uruguay national football team</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00173.json</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
         <v>107</v>
       </c>
@@ -2250,40 +2284,40 @@
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
+    <row r="53" ht="65" customHeight="1">
+      <c r="A53" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>What is the current soccer team of Neymar?</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>Paris Saint-Germain F.C</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Santos F.C.|Santos F.C. (lang:en)</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00122.json</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54">
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
         <v>122</v>
       </c>
@@ -2316,40 +2350,40 @@
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
+    <row r="55" ht="65" customHeight="1">
+      <c r="A55" s="6" t="n">
         <v>127</v>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>What is the name of the father character in the TV series Family Guy?</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Peter Griffin</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>Francis Griffin|Francis Griffin (lang:en)</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00155.json</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
         <v>134</v>
       </c>
@@ -2382,21 +2416,21 @@
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
+    <row r="57" ht="65" customHeight="1">
+      <c r="A57" s="6" t="n">
         <v>139</v>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>What typhoons were of the type super typhoons ?</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>Olive | Emma | Nancy | Violet | Dot | Megi | Songda | Muifa | Nalgae | Guchol | Jelawat | Bopha | Utor | Usagi | Francisco | Lekima | Haiyan | Neoguri | Rammasun | Halong | Genevieve | Phanfone | Vongfong | Nuri | Hagupit | Maysak | Noul | Dolphin | Nangka | Soudelor | Dujuan | Koppu | Meranti | Chaba | Haima | Nock-ten | Noru | Lan | Maria | Jebi | Mangkhut | Trami | Kong-rey | Yutu | Wutip | Hagibis</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>Typhoon Goni|Typhoon Goni (lang:en)
 Typhoon Surigae`|Typhoon Surigae` (lang:en)
@@ -2408,21 +2442,21 @@
 Typhoon Wynne|Typhoon Wynne (lang:en)</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00028.json</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58">
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
         <v>146</v>
       </c>
@@ -2455,40 +2489,40 @@
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
+    <row r="59" ht="65" customHeight="1">
+      <c r="A59" s="6" t="n">
         <v>154</v>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>How many games were played in the National League Championship Series or World Series won by the St. Louis Cardinals that concluded on or after October 16, 1985</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00178.json</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
         <v>162</v>
       </c>
@@ -2521,40 +2555,40 @@
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
+    <row r="61" ht="65" customHeight="1">
+      <c r="A61" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>How many matches Thiago Silva played for played for national team in 2008</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00189.json</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62">
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
         <v>178</v>
       </c>
@@ -2587,21 +2621,21 @@
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
+    <row r="63" ht="65" customHeight="1">
+      <c r="A63" s="6" t="n">
         <v>183</v>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Which weapons are of the type rocket launchers ?</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Bazooka | C90-CR (M3) | FHJ-84 | LRAC F1 | M72 LAW | Nexter WASP 58 Light Anti-Armour Weapon | Panzerfaust 3 | Panzerschreck | PF-89 | PF-98 | Type 70 | VE-NILANGAL</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
         <is>
           <t>M79 Osa|M79 Osa (lang:en)
 Javelot|Javelot (lang:en)
@@ -2615,21 +2649,21 @@
 Zelzal-1|Zelzal-1 (lang:en)</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00031.json</t>
         </is>
       </c>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-    </row>
-    <row r="64">
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
         <v>191</v>
       </c>
@@ -2662,21 +2696,21 @@
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
+    <row r="65" ht="65" customHeight="1">
+      <c r="A65" s="6" t="n">
         <v>199</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Who is or was a member of the 10cc band ?</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Graham Gouldman | Paul Burgess | Rick Fenn | Eric Stewart | Laurence "Lol" Creme | [[Tony OMalley (musician)|Tony OMalley]] | Vic Emerson | Gary Wallis | Mike Stevens</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Iain Hornal|Iain Hornal (lang:en)
 Lol Creme|Lol Creme (lang:en)
@@ -2690,21 +2724,21 @@
 Rick Fenn|Rick Fenn (lang:en)</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00015.json</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr"/>
-      <c r="H65" s="5" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
-    </row>
-    <row r="66">
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
         <v>206</v>
       </c>
@@ -2737,40 +2771,40 @@
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
+    <row r="67" ht="65" customHeight="1">
+      <c r="A67" s="6" t="n">
         <v>211</v>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Who is the author of the The Invisible Man ?</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Ralph Ellison</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>H. G. Wells</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00168.json</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-    </row>
-    <row r="68">
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
         <v>215</v>
       </c>
@@ -2803,40 +2837,40 @@
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
+    <row r="69" ht="65" customHeight="1">
+      <c r="A69" s="6" t="n">
         <v>219</v>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Who is the main character in the film Shawshank Redemption?</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Tim Robbins</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Andy Dufresne</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00028.json</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr"/>
-      <c r="H69" s="5" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr"/>
-    </row>
-    <row r="70">
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
         <v>224</v>
       </c>
@@ -2869,40 +2903,40 @@
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="n">
+    <row r="71" ht="65" customHeight="1">
+      <c r="A71" s="6" t="n">
         <v>228</v>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>What was the label of the song I am not a woman, I’m a god</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Capitol</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>I Am Not a Woman, I'm a God</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00059.json</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr"/>
-      <c r="H71" s="5" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr"/>
+      <c r="I71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
         <v>232</v>
       </c>
@@ -2935,40 +2969,40 @@
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="n">
+    <row r="73" ht="65" customHeight="1">
+      <c r="A73" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>How many titles has Chicago Fire FC won in the US Open Cup</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00173.json</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-    </row>
-    <row r="74">
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
         <v>242</v>
       </c>
@@ -3001,40 +3035,40 @@
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="n">
+    <row r="75" ht="65" customHeight="1">
+      <c r="A75" s="6" t="n">
         <v>246</v>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>How many total games were played across the National League Championship Series competitions that featured both the Los Angeles Dodgers and the Philadelphia Phillies</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00158.json</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr"/>
-    </row>
-    <row r="76">
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
         <v>250</v>
       </c>
@@ -3067,21 +3101,21 @@
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="n">
+    <row r="77" ht="65" customHeight="1">
+      <c r="A77" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>Who played the role of Srikant Tiwari in The Family Man?</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Manoj Bajpayee</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="6" t="inlineStr">
         <is>
           <t>Ashish Warang|Ashish Warang (lang:en)
 Ashlesha Thakur|Ashlesha Thakur (lang:en)
@@ -3095,21 +3129,21 @@
 Sharad Kelkar|Sharad Kelkar (lang:en)</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00227.json</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr"/>
-    </row>
-    <row r="78">
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
         <v>259</v>
       </c>
@@ -3142,40 +3176,40 @@
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="n">
+    <row r="79" ht="65" customHeight="1">
+      <c r="A79" s="6" t="n">
         <v>266</v>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>How old was the New York University actor who played James Dalton in `` The Cooler `` at The Double Deuce when he died</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>P20846D</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00384.json</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
-    </row>
-    <row r="80">
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
         <v>270</v>
       </c>
@@ -3208,21 +3242,21 @@
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
+    <row r="81" ht="65" customHeight="1">
+      <c r="A81" s="6" t="n">
         <v>274</v>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>In the ten countries with the highest HDI, what is the population growth rate along with the male and female suicide rates</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>[['Switzerland', '0.64', '14.2', '9.2'], ['Norway', '0.8% (2022 est.)', '13.4', '7.4'], ['Iceland', '0.89', '18.7', '9.3'], ['Sweden', '0.5% (2022 est.)', '16.9', '8.7'], ['Denmark', '0.44', '11.1', '6.3'], ['Germany', '-0.12', '12.8', '7.6'], ['Ireland', '0.91', '14.3', '4.6'], ['Singapore', '0.9', '12.7', '4.9'], ['Netherlands', '0.36', '12.5', '7.6'], ['Australia', '1.13', '17.0', '6.7']]</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Germany|Germany (lang:en)|0.942|||
 Iceland|Iceland (lang:en)|0.959|||
@@ -3236,21 +3270,21 @@
 Australia|Australia (lang:en)|0.951|||</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_time_complex/00061.json</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
-    </row>
-    <row r="82">
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
         <v>278</v>
       </c>
@@ -3283,21 +3317,21 @@
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
+    <row r="83" ht="65" customHeight="1">
+      <c r="A83" s="6" t="n">
         <v>282</v>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>In which city is each Charles Dickens novel set</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>[['The Pickwick Papers', 'London'], ['Oliver Twist', 'London'], ['The Old Curiosity Shop', 'London'], ['Barnaby Rudge', 'London (Chigwell)'], ['Martin Chuzzlewit', 'London'], ['Bleak House', 'London'], ['Hard Times', 'Coketown'], ['Little Dorrit', 'London'], ['A Tale of Two Cities', 'London'], ['A Tale of Two Cities', 'Paris'], ['Great Expectations', 'Kent'], ['Great Expectations', 'London'], ['Our Mutual Friend', 'London'], ['No Thoroughfare', 'London'], ['The Mystery of Edwin Drood', 'Cloisterham'], ['Nicholas Nickleby', 'London'], ['Dombey and Son', 'London'], ['David Copperfield', 'Blunderstone']]</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Oliver Twist|Oliver Twist (lang:en)|London|London (lang:en)
 Great Expectations|Great Expectations (lang:en)|London|London (lang:en)
@@ -3309,21 +3343,21 @@
 Nicholas Nickleby|Nicholas Nickleby (lang:en)|London|London (lang:en)</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00054.json</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
         <v>288</v>
       </c>
@@ -3356,40 +3390,40 @@
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
+    <row r="85" ht="65" customHeight="1">
+      <c r="A85" s="6" t="n">
         <v>295</v>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>hart of dixie season 4 how many episodes</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Different answer</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Different answer</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00088.json</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr"/>
-      <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
-    </row>
-    <row r="86">
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
         <v>13</v>
       </c>
@@ -3422,21 +3456,21 @@
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="n">
+    <row r="87" ht="65" customHeight="1">
+      <c r="A87" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>For each country in East Asia, return its name and its national dish.</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>[['China', 'Peking duck'], ['Hong Kong', 'Pineapple bun'], ['Hong Kong', 'Dim sum'], ['Macau', 'Minchee'], ['Japan', 'Sushi'], ['Japan', 'Japanese curry'], ['Japan', 'Ramen'], ['Japan', 'Tempura'], ['Japan', 'Wagashi'], ['Japan', 'Sashimi'], ['Japan', 'Miso soup'], ['Mongolia', 'Buuz'], ['North Korea', 'kimchi'], ['South Korea', 'Kimchi'], ['Taiwan', 'Beef noodle soup']]</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>People's Republic of China|People's Republic of China (lang:en)||
 Japan|Japan (lang:en)||
@@ -3446,21 +3480,21 @@
 South Korea|South Korea (lang:en)||</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00079.json</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
-    </row>
-    <row r="88">
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
         <v>52</v>
       </c>
@@ -3493,40 +3527,40 @@
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" s="4" t="n">
+    <row r="89" ht="65" customHeight="1">
+      <c r="A89" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>What was the publication date of the book Adventures of Huckleberry Finn</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>December 10, 1884</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>1884-01-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F89" s="4" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00278.json</t>
         </is>
       </c>
-      <c r="G89" s="5" t="inlineStr"/>
-      <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
-    </row>
-    <row r="90">
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
         <v>75</v>
       </c>
@@ -3566,40 +3600,40 @@
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="n">
+    <row r="91" ht="65" customHeight="1">
+      <c r="A91" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>when does star trek discovery season 1 end</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>February 11, 2018</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>2018-01-01T00:00:00Z</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00514.json</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
-    </row>
-    <row r="92">
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
         <v>113</v>
       </c>
@@ -3632,40 +3666,40 @@
       <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
     </row>
-    <row r="93">
-      <c r="A93" s="4" t="n">
+    <row r="93" ht="65" customHeight="1">
+      <c r="A93" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Where was Hawaii Five-O filmed?</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>Oahu, Hawaii</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Hawaii|Hawaii (lang:en)</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00306.json</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
-    </row>
-    <row r="94">
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
         <v>167</v>
       </c>
@@ -3702,40 +3736,40 @@
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="n">
+    <row r="95" ht="65" customHeight="1">
+      <c r="A95" s="6" t="n">
         <v>205</v>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>who wrote the song after you've gone</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Turner Layton | Henry Creamer</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>Henry Creamer</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F95" s="4" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00497.json</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr"/>
-    </row>
-    <row r="96">
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
         <v>245</v>
       </c>
@@ -3768,40 +3802,40 @@
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="n">
+    <row r="97" ht="65" customHeight="1">
+      <c r="A97" s="6" t="n">
         <v>263</v>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>Who was an ōzeki ?</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>Tachihikari Denemon | Hitachiiwa Eitarō | Toyokuni Fukuma | Shimizugawa Motokichi | Kagamiiwa Zenshirō | Nayoroiwa Shizuo | Saganohana Katsumi | Shionoumi Unemon | Masuiyama Daishirō I | Mitsuneyama Keiji | Ōuchiyama Heikichi | Matsunobori Shigeo | Kotogahama Sadao | Wakahaguro Tomoaki | Kitabayama Hidetoshi | Tochihikari Masayuki | Yutakayama Katsuo | Kiyokuni Katsuo | Maenoyama Tarō | Daikirin Takayoshi | Takanohana Kenshi | Daiju Hisateru | Kaiketsu Masateru | Asahikuni Masuo | Masuiyama Daishirō II | Kotokaze Kōki | Wakashimazu Mutsuo | Asashio Tarō IV | [[Hokutenyū Katsuhiko]] | Konishiki Yasokichi | Kirishima Kazuhiro | Takanonami Sadahiro | Chiyotaikai Ryūji | Dejima Takeharu | Musōyama Masashi | Miyabiyama Tetsushi | Kaiō Hiroyuki | Tochiazuma Daisuke | Kotoōshū Katsunori | Kotomitsuki Keiji | Baruto Kaito | Kotoshōgiku Kazuhiro | Gōeidō Gōtarō | Takayasu Akira | Tochinoshin Tsuyoshi | Takakeishō Mitsunobu | Asanoyama Hideki | Shōdai Naoya</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>Aonishiki Arata|Aonishiki Arata (lang:en)</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00054.json</t>
         </is>
       </c>
-      <c r="G97" s="5" t="inlineStr"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr"/>
-    </row>
-    <row r="98">
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
         <v>291</v>
       </c>
@@ -3835,38 +3869,38 @@
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
     </row>
-    <row r="99">
-      <c r="A99" s="4" t="n">
+    <row r="99" ht="65" customHeight="1">
+      <c r="A99" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>How many games Kevin De Bruyne played for Belgium national football team</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>Temporal changes</t>
         </is>
       </c>
-      <c r="F99" s="4" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00196.json</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I99"/>

--- a/Annotation/annotation_outputs/annotation_group_3.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_3.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -507,11 +507,13 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>case_id</t>
@@ -549,10 +551,20 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>wikidata_cause</t>
+          <t>missing_edge</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>missing_node</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>missing_property_or_qualifier</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -590,6 +602,8 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -623,6 +637,8 @@
       <c r="G3" s="7" t="inlineStr"/>
       <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -656,6 +672,8 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -689,6 +707,8 @@
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -722,6 +742,8 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -755,6 +777,8 @@
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -788,6 +812,8 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -821,6 +847,8 @@
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -854,6 +882,8 @@
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -887,6 +917,8 @@
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -920,6 +952,8 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="65" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -953,6 +987,8 @@
       <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -986,6 +1022,8 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1019,6 +1057,8 @@
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1052,6 +1092,8 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="65" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1085,6 +1127,8 @@
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1118,6 +1162,8 @@
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -1151,6 +1197,8 @@
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1184,6 +1232,8 @@
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="65" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -1217,6 +1267,8 @@
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1250,6 +1302,8 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="65" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1283,6 +1337,8 @@
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1316,6 +1372,8 @@
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="65" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -1349,6 +1407,8 @@
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -1382,6 +1442,8 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="65" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -1415,6 +1477,8 @@
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -1448,6 +1512,8 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="65" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1481,6 +1547,8 @@
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1514,6 +1582,8 @@
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="65" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -1547,6 +1617,8 @@
       <c r="G31" s="7" t="inlineStr"/>
       <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
     </row>
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1580,6 +1652,8 @@
       <c r="G32" s="5" t="inlineStr"/>
       <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="65" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1613,6 +1687,8 @@
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr"/>
     </row>
     <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -1646,6 +1722,8 @@
       <c r="G34" s="5" t="inlineStr"/>
       <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="65" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1679,6 +1757,8 @@
       <c r="G35" s="7" t="inlineStr"/>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr"/>
     </row>
     <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -1712,6 +1792,8 @@
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="65" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -1745,6 +1827,8 @@
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -1778,6 +1862,8 @@
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="65" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -1811,6 +1897,8 @@
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
     </row>
     <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -1853,6 +1941,8 @@
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="65" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1886,6 +1976,8 @@
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -1928,6 +2020,8 @@
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="65" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -1961,6 +2055,8 @@
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+      <c r="K43" s="7" t="inlineStr"/>
     </row>
     <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -1994,6 +2090,8 @@
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="65" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -2027,6 +2125,8 @@
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
     </row>
     <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2069,6 +2169,8 @@
       <c r="G46" s="5" t="inlineStr"/>
       <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="65" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -2110,6 +2212,8 @@
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr"/>
     </row>
     <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
@@ -2149,6 +2253,8 @@
       <c r="G48" s="5" t="inlineStr"/>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="65" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -2184,6 +2290,8 @@
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
     </row>
     <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -2217,6 +2325,8 @@
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="65" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -2250,6 +2360,8 @@
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
     </row>
     <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -2283,6 +2395,8 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="65" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -2316,6 +2430,8 @@
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -2349,6 +2465,8 @@
       <c r="G54" s="5" t="inlineStr"/>
       <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="65" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -2382,6 +2500,8 @@
       <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
     </row>
     <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -2415,6 +2535,8 @@
       <c r="G56" s="5" t="inlineStr"/>
       <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="65" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -2455,6 +2577,8 @@
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -2488,6 +2612,8 @@
       <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="65" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -2521,6 +2647,8 @@
       <c r="G59" s="7" t="inlineStr"/>
       <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
@@ -2554,6 +2682,8 @@
       <c r="G60" s="5" t="inlineStr"/>
       <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="65" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -2587,6 +2717,8 @@
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -2620,6 +2752,8 @@
       <c r="G62" s="5" t="inlineStr"/>
       <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="65" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -2662,6 +2796,8 @@
       <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
@@ -2695,6 +2831,8 @@
       <c r="G64" s="5" t="inlineStr"/>
       <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="65" customHeight="1">
       <c r="A65" s="6" t="n">
@@ -2737,6 +2875,8 @@
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
@@ -2770,6 +2910,8 @@
       <c r="G66" s="5" t="inlineStr"/>
       <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="65" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -2803,6 +2945,8 @@
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2836,6 +2980,8 @@
       <c r="G68" s="5" t="inlineStr"/>
       <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="65" customHeight="1">
       <c r="A69" s="6" t="n">
@@ -2869,6 +3015,8 @@
       <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -2902,6 +3050,8 @@
       <c r="G70" s="5" t="inlineStr"/>
       <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="65" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -2935,6 +3085,8 @@
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -2968,6 +3120,8 @@
       <c r="G72" s="5" t="inlineStr"/>
       <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="65" customHeight="1">
       <c r="A73" s="6" t="n">
@@ -3001,6 +3155,8 @@
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -3034,6 +3190,8 @@
       <c r="G74" s="5" t="inlineStr"/>
       <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="65" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -3067,6 +3225,8 @@
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
@@ -3100,6 +3260,8 @@
       <c r="G76" s="5" t="inlineStr"/>
       <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="65" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -3142,6 +3304,8 @@
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
@@ -3175,6 +3339,8 @@
       <c r="G78" s="5" t="inlineStr"/>
       <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="65" customHeight="1">
       <c r="A79" s="6" t="n">
@@ -3208,6 +3374,8 @@
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+      <c r="K79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -3241,6 +3409,8 @@
       <c r="G80" s="5" t="inlineStr"/>
       <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="65" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -3283,6 +3453,8 @@
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
@@ -3316,6 +3488,8 @@
       <c r="G82" s="5" t="inlineStr"/>
       <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="65" customHeight="1">
       <c r="A83" s="6" t="n">
@@ -3356,6 +3530,8 @@
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
@@ -3389,6 +3565,8 @@
       <c r="G84" s="5" t="inlineStr"/>
       <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="5" t="inlineStr"/>
+      <c r="K84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="65" customHeight="1">
       <c r="A85" s="6" t="n">
@@ -3422,6 +3600,8 @@
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
@@ -3455,6 +3635,8 @@
       <c r="G86" s="5" t="inlineStr"/>
       <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="5" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="65" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -3493,6 +3675,8 @@
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
@@ -3526,6 +3710,8 @@
       <c r="G88" s="5" t="inlineStr"/>
       <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="65" customHeight="1">
       <c r="A89" s="6" t="n">
@@ -3559,6 +3745,8 @@
       <c r="G89" s="7" t="inlineStr"/>
       <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
     </row>
     <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -3599,6 +3787,8 @@
       <c r="G90" s="5" t="inlineStr"/>
       <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="65" customHeight="1">
       <c r="A91" s="6" t="n">
@@ -3632,6 +3822,8 @@
       <c r="G91" s="7" t="inlineStr"/>
       <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
     </row>
     <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
@@ -3665,6 +3857,8 @@
       <c r="G92" s="5" t="inlineStr"/>
       <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="5" t="inlineStr"/>
+      <c r="K92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="65" customHeight="1">
       <c r="A93" s="6" t="n">
@@ -3698,6 +3892,8 @@
       <c r="G93" s="7" t="inlineStr"/>
       <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
@@ -3735,6 +3931,8 @@
       <c r="G94" s="5" t="inlineStr"/>
       <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="5" t="inlineStr"/>
+      <c r="K94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="65" customHeight="1">
       <c r="A95" s="6" t="n">
@@ -3768,6 +3966,8 @@
       <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
     </row>
     <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -3801,6 +4001,8 @@
       <c r="G96" s="5" t="inlineStr"/>
       <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="5" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="65" customHeight="1">
       <c r="A97" s="6" t="n">
@@ -3834,6 +4036,8 @@
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
@@ -3868,6 +4072,8 @@
       <c r="G98" s="5" t="inlineStr"/>
       <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="5" t="inlineStr"/>
+      <c r="K98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="65" customHeight="1">
       <c r="A99" s="6" t="n">
@@ -3901,15 +4107,17 @@
       <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I99"/>
+  <autoFilter ref="A1:K99"/>
   <dataValidations count="2">
     <dataValidation sqref="G2:G99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Correct,Incorrect,Unsure"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Missing edge,Missing node,Missing property/qualifier,Not applicable,Unsure"</formula1>
+    <dataValidation sqref="H2:H99 I2:I99 J2:J99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Annotation/annotation_outputs/annotation_group_3.xlsx
+++ b/Annotation/annotation_outputs/annotation_group_3.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$M$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -497,20 +497,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -536,35 +538,45 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>SPARQL</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Corrected SPARQL</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>taxonomy_label</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>label_correctness</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>missing_edge</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>missing_node</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>missing_property_or_qualifier</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -591,19 +603,31 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?location ?locationLabel WHERE {
+  wd:Q23572 wdt:P915 ?location .
+  OPTIONAL {
+    ?location rdfs:label ?locationLabel
+    FILTER(LANG(?locationLabel) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00711.json</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="65" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -626,19 +650,34 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?club ?clubLabel WHERE {
+  wd:Q131261 p:P54 ?membership .
+  ?membership ps:P54 ?club .
+  ?membership pq:P580 ?start .
+  ?membership pq:P582 ?end .
+  FILTER(?start &lt;= "2001-12-31T23:59:59Z" ^^ xsd:dateTime &amp;&amp; ?end &gt;= "2001-01-01T00:00:00Z" ^^ xsd:dateTime)
+  .
+  ?club rdfs:label ?clubLabel .
+  FILTER(LANG(?clubLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00033.json</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr"/>
       <c r="I3" s="7" t="inlineStr"/>
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="65" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -661,19 +700,31 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?actorLabel WHERE {
+  wd:Q451603 wdt:P161 ?actor .
+  OPTIONAL {
+    ?actor rdfs:label ?actorLabel
+    FILTER(LANG(?actorLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00609.json</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="65" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -696,19 +747,31 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?director ?directorLabel WHERE {
+  wd:Q110779028 wdt:P179 / wdt:P57 ?director .
+  OPTIONAL {
+    ?director rdfs:label ?directorLabel .
+    FILTER(lang(?directorLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00136.json</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="65" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -731,19 +794,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?company WHERE {
+  wd:Q2947967 wdt:P272 ?company
+}</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00289.json</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="65" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -766,19 +837,34 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel WHERE {
+  wd:Q624 p:P54 ?membership .
+  ?membership ps:P54 ?team .
+  ?membership pq:P580 ?start .
+  ?membership pq:P582 ?end .
+  ?team rdfs:label ?teamLabel .
+  FILTER(LANG(?teamLabel) = "en")
+  FILTER(YEAR(?start) &lt;= 2014)
+  FILTER(YEAR(?end) &gt;= 2012)
+}</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00114.json</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="7" t="inlineStr"/>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -801,19 +887,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor WHERE {
+  wd:Q1781831 wdt:P161 ?actor
+}</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00613.json</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="65" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -836,19 +930,31 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?owner ?ownerLabel WHERE {
+  wd:Q1368043 wdt:P127 ?owner .
+  OPTIONAL {
+    ?owner rdfs:label ?ownerLabel
+    FILTER(lang(?ownerLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00520.json</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr"/>
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="65" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -871,19 +977,32 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?actorLabel WHERE {
+  wd:Q502629 wdt:P161 ?actor .
+  OPTIONAL {
+    ?actor rdfs:label ?actorLabel
+    FILTER(LANG(?actorLabel) = "en")
+    .
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00920.json</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="65" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -906,19 +1025,28 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor WHERE {
+  wd:Q28443710 p:P161 ?statement .
+  ?statement ps:P161 ?actor ; pq:P453 wd:Q65921603 .
+}</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00140.json</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr"/>
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="65" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -941,19 +1069,27 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?broadcaster WHERE {
+  wd:Q15104549 wdt:P449 ?broadcaster
+}</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00123.json</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
       <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="65" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -976,19 +1112,30 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?award WHERE {
+  wd:Q44183 p:P166 ?statement .
+  ?statement ps:P166 ?award .
+  ?statement pq:P585 ?time .
+  FILTER(YEAR(?time) = 1983)
+}</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00126.json</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="65" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1011,19 +1158,32 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?club ?clubLabel WHERE {
+  wd:Q266613 p:P54 ?statement .
+  ?statement ps:P54 ?club ; pq:P580 ?start ; pq:P582 ?end .
+  FILTER(YEAR(?start) &lt;= 2003 &amp;&amp; YEAR(?end) &gt;= 2003)
+  .
+  ?club rdfs:label ?clubLabel .
+  FILTER(LANG(?clubLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00079.json</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1046,19 +1206,34 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?club ?clubLabel(MAX(xsd:integer(?goalsRaw)) AS ?maxGoals) WHERE {
+  wd:Q17515 p:P54 ?club_statement .
+  ?club_statement ps:P54 ?club ; pq:P1351 ?goalsRaw .
+  FILTER(isNumeric(xsd:integer(?goalsRaw)))
+  ?club rdfs:label ?clubLabel .
+  FILTER(LANG(?clubLabel) = 'en')
+}
+GROUP BY ?club ?clubLabel
+ORDER BY DESC(?maxGoals)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00170.json</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="65" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1081,19 +1256,30 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?book ?date WHERE {
+  wd:Q129240 wdt:P527 ?book .
+  ?book wdt:P577 ?date .
+}
+ORDER BY ?date
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00068.json</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="65" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1116,19 +1302,33 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?club ?clubLabel WHERE {
+  wd:Q185572 p:P54 ?statement .
+  ?statement ps:P54 ?club .
+  ?statement pq:P580 ?start .
+  ?statement pq:P582 ?end .
+  FILTER(YEAR(?start) &lt;= 2003 &amp;&amp; YEAR(?end) &gt;= 2003)
+  ?club rdfs:label ?clubLabel .
+  FILTER(LANG(?clubLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00066.json</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="65" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1151,19 +1351,32 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?performer ?performerLabel WHERE {
+  wd:Q2264239 wdt:P175 ?performer .
+  OPTIONAL {
+    ?performer rdfs:label ?performerLabel
+    FILTER(LANG(?performerLabel) = "en")
+    .
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00957.json</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
       <c r="K18" s="5" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="65" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -1186,19 +1399,33 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?movieLabel ?releaseDate WHERE {
+  ?movie wdt:P58 wd:Q963032 .
+  ?movie wdt:P31 wd:Q11424 .
+  ?movie wdt:P577 ?releaseDate .
+  ?movie rdfs:label ?movieLabel .
+  FILTER(LANG(?movieLabel) = "en")
+}
+ORDER BY ASC(?releaseDate)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00275.json</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
       <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="65" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1221,19 +1448,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?screenwriter WHERE {
+  wd:Q485803 wdt:P58 ?screenwriter .
+}</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00034.json</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
       <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="65" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -1256,19 +1491,36 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?title ?date WHERE {
+  ?movie wdt:P161 wd:Q37628 .
+  ?movie wdt:P31 wd:Q11424 .
+  ?movie wdt:P577 ?date .
+  ?movie rdfs:label ?title .
+  FILTER(lang(?title) = 'en')
+  .
+  FILTER(DATATYPE(?date) = xsd:dateTime)
+  .
+}
+ORDER BY ?date
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00038.json</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="65" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1291,19 +1543,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?state ?stateLabel(COUNT(?plant) AS ?count) WHERE {
+  ?plant wdt:P31 wd:Q30565277 .
+  ?plant wdt:P17 wd:Q30 .
+  ?plant wdt:P131 * ?state .
+  ?state wdt:P31 / wdt:P279 * wd:Q35657 .
+  ?state rdfs:label ?stateLabel .
+  FILTER(LANG(?stateLabel) = "en")
+}
+GROUP BY ?state ?stateLabel
+ORDER BY DESC(?count)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00291.json</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
       <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="65" customHeight="1">
       <c r="A23" s="6" t="n">
@@ -1326,19 +1594,33 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?book ?bookLabel ?pubDate WHERE {
+  wd:Q2512889 wdt:P527 ?book .
+  ?book rdfs:label ?bookofLabel .
+  FILTER(LANG(?bookofLabel) = 'en')
+  .
+  ?book wdt:P577 ?pubDate .
+}
+ORDER BY(?pubDate)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00093.json</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24" ht="65" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1361,19 +1643,33 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel(COUNT(*) AS ?wins) WHERE {
+  ?superbowl wdt:P31 wd:Q32096 .
+  ?superbowl wdt:P1346 ?team .
+  ?team rdfs:label ?teamLabel .
+  FILTER(lang(?teamLabel) = "en")
+}
+GROUP BY ?team ?teamLabel
+ORDER BY DESC(?wins)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00716.json</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
       <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="65" customHeight="1">
       <c r="A25" s="6" t="n">
@@ -1396,19 +1692,34 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?runtime ?label WHERE {
+  VALUES ?movie {
+    wd:Q752313 wd:Q843612 wd:Q11909982
+  }
+  ?movie wdt:P2047 ?runtime .
+  ?movie rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}
+ORDER BY DESC(?runtime)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00141.json</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26" ht="65" customHeight="1">
       <c r="A26" s="4" t="n">
@@ -1431,19 +1742,31 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?state ?date WHERE {
+  ?state wdt:P31 wd:Q35657 .
+  ?state wdt:P571 ?date .
+  FILTER(DATATYPE(?date) = xsd:dateTime)
+}
+ORDER BY DESC(?date)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00420.json</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="65" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -1466,19 +1789,33 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?series ?seriesLabel WHERE {
+  ?series wdt:P161 wd:Q103939 .
+  ?series wdt:P170 wd:Q430844 .
+  ?series wdt:P31 wd:Q5398426 .
+  OPTIONAL {
+    ?series rdfs:label ?seriesLabel .
+    FILTER(LANG(?seriesLabel) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00292.json</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28" ht="65" customHeight="1">
       <c r="A28" s="4" t="n">
@@ -1501,19 +1838,32 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?album ?year WHERE {
+  VALUES ?album {
+    wd:Q190989 wd:Q187507
+  }
+  ?album wdt:P577 ?date .
+  BIND(YEAR(?date) AS ?year)
+}
+ORDER BY ?year</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00103.json</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="5" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="65" customHeight="1">
       <c r="A29" s="6" t="n">
@@ -1536,19 +1886,32 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?movie ?movieLabel ?runtime WHERE {
+  VALUES ?movie {
+    wd:Q27178 wd:Q2875
+  }
+  ?movie wdt:P2047 ?runtime .
+  ?movie rdfs:label ?movieLabel .
+  FILTER(LANG(?movieLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00254.json</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30" ht="65" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -1571,19 +1934,30 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?city ?population WHERE {
+  wd:Q1371 wdt:P36 ?city .
+  ?city wdt:P1082 ?population .
+}
+ORDER BY DESC(?population)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00756.json</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="65" customHeight="1">
       <c r="A31" s="6" t="n">
@@ -1606,19 +1980,31 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?work ?workLabel WHERE {
+  wd:Q314176 wdt:P800 ?work .
+  OPTIONAL {
+    ?work rdfs:label ?workLabel .
+    FILTER(LANG(?workLabel) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00027.json</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32" ht="65" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1641,19 +2027,29 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?director ?directorLabel WHERE {
+  wd:Q103372692 wdt:P57 ?director .
+  ?director rdfs:label ?directorLabel .
+  FILTER(LANG(?directorLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00152.json</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="65" customHeight="1">
       <c r="A33" s="6" t="n">
@@ -1676,19 +2072,27 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?release_date WHERE {
+  wd:Q506418 wdt:P577 ?release_date .
+}</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00893.json</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
     </row>
     <row r="34" ht="65" customHeight="1">
       <c r="A34" s="4" t="n">
@@ -1711,19 +2115,30 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?drummer ?label WHERE {
+  wd:Q11895 wdt:P527 ?drummer .
+  ?drummer wdt:P106 wd:Q386854 .
+  ?drummer rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00559.json</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
       <c r="K34" s="5" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="65" customHeight="1">
       <c r="A35" s="6" t="n">
@@ -1746,19 +2161,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?director ?name WHERE {
+  ?film wdt:P179 wd:Q388659 ; wdt:P57 ?director ; wdt:P577 ?date .
+  ?director rdfs:label ?name .
+  FILTER(LANG(?name) = 'en')
+  .
+}
+ORDER BY ?date
+LIMIT 4</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00034.json</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
     </row>
     <row r="36" ht="65" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -1781,19 +2209,29 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?actorLabel WHERE {
+  wd:Q16867394 wdt:P161 ?actor .
+  ?actor rdfs:label ?actorLabel .
+  FILTER(LANG(?actorLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in KG than in Table</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00106.json</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
       <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="65" customHeight="1">
       <c r="A37" s="6" t="n">
@@ -1816,19 +2254,28 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?match) AS ?wins) WHERE {
+  ?match wdt:P710 wd:Q47774 ; wdt:P585 ?date ; wdt:P1346 wd:Q47774 .
+  FILTER(?date &gt; "2018-07-15T00:00:00Z" ^^ xsd:dateTime)
+}</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00033.json</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38" ht="65" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -1851,19 +2298,40 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?prisonLabel WHERE {
+  {
+    SELECT ?prisoner WHERE {
+      ?event wdt:P31 wd:Q598041 ; wdt:P710 ?prisoner .
+    }
+    GROUP BY ?prisoner
+    HAVING(COUNT(?event) &gt;= 2)
+  }
+  ?escapeEvent wdt:P31 wd:Q598041 ; wdt:P710 ?prisoner ; wdt:P276 ?prison .
+  OPTIONAL {
+    ?prison rdfs:label ?prisonLabel
+    FILTER(LANG(?prisonLabel) = 'en')
+    .
+  }
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00056.json</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
       <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="65" customHeight="1">
       <c r="A39" s="6" t="n">
@@ -1886,19 +2354,32 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?olympics) AS ?count) WHERE {
+  ?competition wdt:P1346 wd:Q334526 .
+  ?competition wdt:P641 wd:Q37019 .
+  ?competition wdt:P361 ?olympics .
+  ?olympics wdt:P31 wd:Q20200 .
+  ?olympics wdt:P585 ?date .
+  FILTER(xsd:dateTime(?date) &lt;= "2020-12-31T23:59:59Z" ^^ xsd:dateTime)
+}</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00039.json</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
       <c r="I39" s="7" t="inlineStr"/>
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40" ht="65" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -1930,19 +2411,31 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?occupation ?occupationLabel WHERE {
+  wd:Q83287 wdt:P106 ?occupation .
+  OPTIONAL {
+    ?occupation rdfs:label ?occupationLabel
+    FILTER(lang(?occupationLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00166.json</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
       <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="65" customHeight="1">
       <c r="A41" s="6" t="n">
@@ -1965,19 +2458,28 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor WHERE {
+  wd:Q1418559 wdt:P161 ?actor .
+  FILTER(?actor = wd:Q239786)
+}</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00279.json</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
     <row r="42" ht="65" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -2009,19 +2511,35 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?bridge ?bridgeLabel ?height WHERE {
+  ?bridge wdt:P31 / wdt:P279 * wd:Q12280 .
+  ?bridge wdt:P2793 ?height .
+  FILTER(?height &gt;= 200)
+  OPTIONAL {
+    ?bridge rdfs:label ?bridgeLabel
+    FILTER(LANG(?bridgeLabel) = 'en')
+  }
+}
+ORDER BY DESC(?height)
+LIMIT 10</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00002.json</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
       <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="5" t="inlineStr"/>
     </row>
     <row r="43" ht="65" customHeight="1">
       <c r="A43" s="6" t="n">
@@ -2044,19 +2562,31 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?award) AS ?count) WHERE {
+  wd:Q171669 wdt:P166 ?award .
+  ?award rdfs:label ?label .
+  FILTER(CONTAINS(LCASE(?label) , "golden globe"))
+  .
+  FILTER(LANG(?label) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00139.json</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
       <c r="K43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44" ht="65" customHeight="1">
       <c r="A44" s="4" t="n">
@@ -2079,19 +2609,33 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?breed ?breedLabel WHERE {
+  ?breed wdt:P31 / wdt:P279 * wd:Q39367 .
+  ?breed wdt:P8556 ?extinctionDate .
+  OPTIONAL {
+    ?breed rdfs:label ?breedLabel .
+    FILTER(LANG(?breedLabel) = "en")
+  }
+}
+LIMIT 50</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00061.json</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
       <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr"/>
     </row>
     <row r="45" ht="65" customHeight="1">
       <c r="A45" s="6" t="n">
@@ -2114,19 +2658,28 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?count) WHERE {
+  ?cup wdt:P31 wd:Q19317 ; wdt:P1346 wd:Q676899 ; wdt:P582 ?endDate .
+  FILTER(YEAR(?endDate) &lt; 2006)
+}</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00043.json</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
     </row>
     <row r="46" ht="65" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2158,19 +2711,34 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?item ?label WHERE {
+  ?item wdt:P279 + wd:Q641196 .
+  OPTIONAL {
+    ?item rdfs:label ?label
+    FILTER(lang(?label) = "en")
+    .
+  }
+  FILTER(CONTAINS(LCASE(?label) , "recoilless") || CONTAINS(LCASE(?label) , "rcl"))
+}
+ORDER BY ?label</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00060.json</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
       <c r="K46" s="5" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="5" t="inlineStr"/>
     </row>
     <row r="47" ht="65" customHeight="1">
       <c r="A47" s="6" t="n">
@@ -2201,19 +2769,38 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?item ?name WHERE {
+  ?item wdt:P31 / wdt:P279 * wd:Q2488 .
+  OPTIONAL {
+    ?item rdfs:label ?name .
+    FILTER(LANG(?name) = "en")
+  }
+  OPTIONAL {
+    ?item skos:altLabel ?name .
+    FILTER(LANG(?name) = "en")
+  }
+  FILTER(BOUND(?name))
+  FILTER(REGEX(?name , "Sombrero|Whirlpool|Pinwheel|Surfboard|Andromeda|Centaurus|Triangulum|Cartwheel|Black Eye|Sunflower|Cigar|Comet|Butterfly|Antennae|Tadpole|Sculptor|Sailboat" , "i"))
+}
+LIMIT 15</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00057.json</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
     </row>
     <row r="48" ht="65" customHeight="1">
       <c r="A48" s="4" t="n">
@@ -2242,19 +2829,30 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?promotion ?label WHERE {
+  ?promotion wdt:P31 wd:Q721067 .
+  ?promotion wdt:P641 wd:Q11446353 .
+  ?promotion rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00021.json</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
       <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr"/>
     </row>
     <row r="49" ht="65" customHeight="1">
       <c r="A49" s="6" t="n">
@@ -2279,19 +2877,31 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?award ?label WHERE {
+  ?award wdt:P31 / wdt:P279 * wd:Q618779 .
+  ?award rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+  .
+  FILTER(CONTAINS(LCASE(?label) , "national quality award"))
+}</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00010.json</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
       <c r="J49" s="7" t="inlineStr"/>
       <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
     </row>
     <row r="50" ht="65" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -2314,19 +2924,32 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
+          <t>SELECT(SUM(?dodgersWins) AS ?totalWins) WHERE {
+  VALUES ?series {
+    wd:Q1004352 wd:Q1004228 wd:Q3511262 wd:Q3511261
+  }
+  ?series wdt:P1346 ?winner ; wdt:P5504 ?games .
+  BIND(IF(?series IN(wd:Q1004352 , wd:Q1004228) , 3 , 4) AS ?requiredWins)
+  BIND(IF(?winner = wd:Q334634 , ?requiredWins , ?games - ?requiredWins) AS ?dodgersWins)
+}</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00165.json</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
       <c r="K50" s="5" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="65" customHeight="1">
       <c r="A51" s="6" t="n">
@@ -2349,19 +2972,27 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?nationalTeam WHERE {
+  wd:Q26517 wdt:P1532 ?nationalTeam
+}</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00173.json</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr"/>
       <c r="J51" s="7" t="inlineStr"/>
       <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
     </row>
     <row r="52" ht="65" customHeight="1">
       <c r="A52" s="4" t="n">
@@ -2384,19 +3015,27 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?country WHERE {
+  wd:Q880092 wdt:P495 ?country
+}</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00138.json</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="5" t="inlineStr"/>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
       <c r="K52" s="5" t="inlineStr"/>
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="5" t="inlineStr"/>
     </row>
     <row r="53" ht="65" customHeight="1">
       <c r="A53" s="6" t="n">
@@ -2419,19 +3058,41 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel WHERE {
+  wd:Q142794 p:P54 ?statement .
+  ?statement ps:P54 ?team .
+  ?team wdt:P31 / wdt:P279 * wd:Q476028 .
+  FILTER NOT EXISTS {
+    ?statement pq:P582 []
+  }
+  .
+  OPTIONAL {
+    ?statement pq:P580 ?startTime
+  }
+  .
+  ?team rdfs:label ?teamLabel .
+  FILTER(LANG(?teamLabel) = 'en')
+}
+ORDER BY DESC(?startTime)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00122.json</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
       <c r="J53" s="7" t="inlineStr"/>
       <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="65" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -2454,19 +3115,31 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?game) AS ?count) WHERE {
+  VALUES ?series {
+    wd:Q3511178 wd:Q14870260 wd:Q56692089
+  }
+  ?game wdt:P361 ?series .
+  ?game wdt:P276 wd:Q49136 .
+}</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00152.json</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
       <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr"/>
+      <c r="M54" s="5" t="inlineStr"/>
     </row>
     <row r="55" ht="65" customHeight="1">
       <c r="A55" s="6" t="n">
@@ -2489,19 +3162,31 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?character ?label WHERE {
+  wd:Q5930 wdt:P674 ?character .
+  ?character rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+  FILTER(CONTAINS(?label , "Francis"))
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00155.json</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
     </row>
     <row r="56" ht="65" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -2524,19 +3209,37 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
+          <t>SELECT(SUM(xsd:integer(?wins)) AS ?total_games) WHERE {
+  ?series wdt:P31 wd:Q1363275 ; wdt:P1923 wd:Q334634 ; wdt:P1923 wd:Q650840 ; wdt:P585 ?date .
+  {
+    ?series p:P1366 / ps:P1366 ?team ; p:P1366 / pq:P1267 ?wins .
+  } UNION {
+    ?series p:P1367 / ps:P1367 ?team ; p:P1367 / pq:P1267 ?wins .
+  }
+  VALUES ?team {
+    wd:Q334634 wd:Q650840
+  }
+  BIND(xsd:integer(SUBSTR(STR(?date) , 1 , 4)) AS ?year)
+  FILTER(?year &gt;= 1978 &amp;&amp; ?year &lt;= 2009)
+}</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00195.json</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr"/>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
       <c r="K56" s="5" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="5" t="inlineStr"/>
     </row>
     <row r="57" ht="65" customHeight="1">
       <c r="A57" s="6" t="n">
@@ -2566,19 +3269,31 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?typhoon ?label WHERE {
+  ?typhoon wdt:P31 wd:Q15941028 .
+  OPTIONAL {
+    ?typhoon rdfs:label ?label .
+    FILTER(LANG(?label) = 'en')
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00028.json</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr"/>
       <c r="J57" s="7" t="inlineStr"/>
       <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
     </row>
     <row r="58" ht="65" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -2601,19 +3316,30 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
+          <t>SELECT(SUM(?games) AS ?totalGames) WHERE {
+  ?edition wdt:P31 wd:Q1363275 .
+  ?edition wdt:P710 wd:Q334634 .
+  ?edition wdt:P710 wd:Q650840 .
+  ?edition wdt:P1350 ?games .
+}</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00099.json</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr"/>
     </row>
     <row r="59" ht="65" customHeight="1">
       <c r="A59" s="6" t="n">
@@ -2636,19 +3362,32 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
+          <t>SELECT(SUM(?games) AS ?totalGames) WHERE {
+  VALUES ?seriesType {
+    wd:Q300972 wd:Q20206337
+  }
+  ?edition wdt:P31 ?seriesType ; wdt:P1346 ?winnerSeason ; wdt:P582 ?endDate ; wdt:P1350 ?games .
+  ?winnerSeason wdt:P54 wd:Q504309 .
+  FILTER(xsd:date(?endDate) &gt;= "1985-10-16" ^^ xsd:date)
+}</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00178.json</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr"/>
       <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="65" customHeight="1">
       <c r="A60" s="4" t="n">
@@ -2671,19 +3410,34 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(DISTINCT ?event) AS ?count) WHERE {
+  wd:Q334526 p:P1344 ?participation .
+  ?participation ps:P1344 ?event .
+  ?participation pq:P1349 wd:Q1985727 .
+  ?event wdt:P361 ?olympics .
+  ?olympics wdt:P31 wd:Q20200 .
+  ?olympics wdt:P585 ?date .
+  ?event wdt:P641 wd:Q2739 .
+  FILTER(YEAR(?date) &lt;= 2020)
+}</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00041.json</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr"/>
     </row>
     <row r="61" ht="65" customHeight="1">
       <c r="A61" s="6" t="n">
@@ -2706,19 +3460,29 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?event) AS ?count) WHERE {
+  wd:Q210453 wdt:P1344 ?event .
+  ?event wdt:P585 ?date .
+  FILTER(YEAR(?date) = 2008)
+}</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00189.json</t>
         </is>
       </c>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
       <c r="J61" s="7" t="inlineStr"/>
       <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
     </row>
     <row r="62" ht="65" customHeight="1">
       <c r="A62" s="4" t="n">
@@ -2741,19 +3505,28 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?match) AS ?count) WHERE {
+  ?match wdt:P31 wd:Q1354208 ; wdt:P585 ?date ; wdt:P710 wd:Q43310 ; wdt:P1923 wd:Q4457 .
+  FILTER(STRSTARTS(STR(?date) , "1965"))
+}</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00127.json</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr"/>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="5" t="inlineStr"/>
     </row>
     <row r="63" ht="65" customHeight="1">
       <c r="A63" s="6" t="n">
@@ -2785,19 +3558,34 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?weapon ?weaponLabel WHERE {
+  {
+    ?weapon wdt:P279 * wd:Q3216918
+  } UNION {
+    ?weapon wdt:P279 * wd:Q506219
+  }
+  ?weapon rdfs:label ?weaponLabel .
+  FILTER(LANG(?weaponLabel) = "en")
+}
+LIMIT 10</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00031.json</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
       <c r="J63" s="7" t="inlineStr"/>
       <c r="K63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="65" customHeight="1">
       <c r="A64" s="4" t="n">
@@ -2820,19 +3608,41 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?team ?teamLabel WHERE {
+  wd:Q142794 p:P54 ?statement .
+  ?statement ps:P54 ?team . MINUS {
+    ?statement pq:P582 ?endTime
+  }
+  . MINUS {
+    ?team wdt:P31 wd:Q15294891
+  }
+  .
+  OPTIONAL {
+    ?statement pq:P580 ?startTime
+  }
+  ?team rdfs:label ?teamLabel .
+  FILTER(LANG(?teamLabel) = 'en')
+}
+ORDER BY DESC(?startTime)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00164.json</t>
         </is>
       </c>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="5" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="5" t="inlineStr"/>
     </row>
     <row r="65" ht="65" customHeight="1">
       <c r="A65" s="6" t="n">
@@ -2864,19 +3674,29 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?member ?label WHERE {
+  ?member wdt:P463 wd:Q169145 .
+  ?member rdfs:label ?label .
+  FILTER(LANG(?label) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00015.json</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
       <c r="J65" s="7" t="inlineStr"/>
       <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="65" customHeight="1">
       <c r="A66" s="4" t="n">
@@ -2899,19 +3719,29 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?population WHERE {
+  wd:Q229104 wdt:P27 wd:Q17 .
+  wd:Q17 wdt:P36 wd:Q1490 .
+  wd:Q1490 wdt:P1082 ?population .
+}</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00162.json</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
       <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="5" t="inlineStr"/>
     </row>
     <row r="67" ht="65" customHeight="1">
       <c r="A67" s="6" t="n">
@@ -2934,19 +3764,27 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?author WHERE {
+  wd:Q1539509 wdt:P50 ?author
+}</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00168.json</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr"/>
       <c r="J67" s="7" t="inlineStr"/>
       <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="65" customHeight="1">
       <c r="A68" s="4" t="n">
@@ -2969,19 +3807,32 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?coach ?coachLabel WHERE {
+  wd:Q308683 wdt:P286 ?coach .
+  OPTIONAL {
+    ?coach rdfs:label ?coachLabel
+    FILTER(lang(?coachLabel) = 'en')
+    .
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00040.json</t>
         </is>
       </c>
-      <c r="G68" s="5" t="inlineStr"/>
-      <c r="H68" s="5" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr"/>
+      <c r="M68" s="5" t="inlineStr"/>
     </row>
     <row r="69" ht="65" customHeight="1">
       <c r="A69" s="6" t="n">
@@ -3004,19 +3855,31 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?character WHERE {
+  ?character wdt:P1441 wd:Q172241 .
+  ?character wdt:P31 ?type .
+  VALUES ?type {
+    wd:Q5 wd:Q15773347
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00028.json</t>
         </is>
       </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
       <c r="J69" s="7" t="inlineStr"/>
       <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="65" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -3039,19 +3902,34 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?album ?albumLabel WHERE {
+  ?album wdt:P175 wd:Q134541 ; wdt:P264 wd:Q231694 ; wdt:P577 ?date .
+  OPTIONAL {
+    ?album rdfs:label ?albumLabel
+    FILTER(lang(?albumLabel) = "en")
+    .
+  }
+}
+ORDER BY ASC(?date)
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00146.json</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr"/>
-      <c r="H70" s="5" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="5" t="inlineStr"/>
+      <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="65" customHeight="1">
       <c r="A71" s="6" t="n">
@@ -3074,19 +3952,28 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?label WHERE {
+  wd:Q108822278 rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00059.json</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
       <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="65" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -3109,19 +3996,29 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?awardLabel WHERE {
+  wd:Q7579596 rdfs:label ?awardLabel .
+  FILTER(LANG(?awardLabel) = 'en')
+}
+LIMIT 1</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00367.json</t>
         </is>
       </c>
-      <c r="G72" s="5" t="inlineStr"/>
-      <c r="H72" s="5" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="5" t="inlineStr"/>
     </row>
     <row r="73" ht="65" customHeight="1">
       <c r="A73" s="6" t="n">
@@ -3144,19 +4041,31 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(*) AS ?count) WHERE {
+  ?cupEdition wdt:P1346 wd:Q308683 .
+  ?cupEdition rdfs:label ?label .
+  FILTER(LANG(?label) = "en")
+  .
+  FILTER REGEX(?label , "US Open Cup" , "i")
+}</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00173.json</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
       <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="65" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -3179,19 +4088,27 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?award) AS ?totalAwards) WHERE {
+  wd:Q147235 wdt:P166 ?award .
+}</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00028.json</t>
         </is>
       </c>
-      <c r="G74" s="5" t="inlineStr"/>
-      <c r="H74" s="5" t="inlineStr"/>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="5" t="inlineStr"/>
     </row>
     <row r="75" ht="65" customHeight="1">
       <c r="A75" s="6" t="n">
@@ -3214,19 +4131,33 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
+          <t>SELECT(SUM(xsd:integer(?gamesAmount)) AS ?totalGames) WHERE {
+  ?edition wdt:P179 wd:Q1363275 .
+  {
+    ?edition wdt:P1345 wd:Q650840 ; wdt:P1346 wd:Q334634 ; p:P482 / psv:P482 ?gamesNode .
+  } UNION {
+    ?edition wdt:P1345 wd:Q334634 ; wdt:P1346 wd:Q650840 ; p:P482 / psv:P482 ?gamesNode .
+  }
+  ?gamesNode wikibase:quantityAmount ?gamesAmount .
+}</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Sportsreason_TANQ_complex/00158.json</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr"/>
       <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="65" customHeight="1">
       <c r="A76" s="4" t="n">
@@ -3249,19 +4180,27 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?track) AS ?count) WHERE {
+  wd:Q1110592 wdt:P658 ?track
+}</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00206.json</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr"/>
-      <c r="H76" s="5" t="inlineStr"/>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
       <c r="K76" s="5" t="inlineStr"/>
+      <c r="L76" s="5" t="inlineStr"/>
+      <c r="M76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="65" customHeight="1">
       <c r="A77" s="6" t="n">
@@ -3293,19 +4232,29 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?actor ?actorLabel WHERE {
+  wd:Q85807149 wdt:P161 ?actor .
+  ?actor rdfs:label ?actorLabel .
+  FILTER(LANG(?actorLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00227.json</t>
         </is>
       </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="65" customHeight="1">
       <c r="A78" s="4" t="n">
@@ -3328,19 +4277,34 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?person ?personLabel WHERE {
+  ?person wdt:P31 wd:Q5 .
+  ?person schema:description ?desc .
+  FILTER(LANG(?desc) = 'en')
+  .
+  FILTER(CONTAINS(LCASE(?desc) , 'nuclear whistleblower'))
+  .
+  ?person rdfs:label ?personLabel .
+  FILTER(LANG(?personLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00023.json</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr"/>
-      <c r="H78" s="5" t="inlineStr"/>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="5" t="inlineStr"/>
       <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="5" t="inlineStr"/>
     </row>
     <row r="79" ht="65" customHeight="1">
       <c r="A79" s="6" t="n">
@@ -3363,19 +4327,28 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
+          <t>SELECT(?deathDate - ?birthDate AS ?age) WHERE {
+  wd:Q49004 wdt:P569 ?birthDate .
+  wd:Q49004 wdt:P570 ?deathDate
+}</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00384.json</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
       <c r="I79" s="7" t="inlineStr"/>
       <c r="J79" s="7" t="inlineStr"/>
       <c r="K79" s="7" t="inlineStr"/>
+      <c r="L79" s="7" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="65" customHeight="1">
       <c r="A80" s="4" t="n">
@@ -3398,19 +4371,30 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?previousShow ?previousShowLabel WHERE {
+  wd:Q928149 rdfs:label ?previousShowLabel .
+  FILTER(LANG(?previousShowLabel) = "en")
+  .
+  BIND(wd:Q928149 AS ?previousShow)
+}</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00068.json</t>
         </is>
       </c>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr"/>
       <c r="K80" s="5" t="inlineStr"/>
+      <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="5" t="inlineStr"/>
     </row>
     <row r="81" ht="65" customHeight="1">
       <c r="A81" s="6" t="n">
@@ -3442,19 +4426,51 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?country ?countryLabel ?hdi ?popGrowthRate ?maleSuicideRate ?femaleSuicideRate WHERE {
+  {
+    SELECT ?country(xsd:double(?hdi_val) AS ?hdi) WHERE {
+      ?country wdt:P31 wd:Q6256 .
+      ?country wdt:P1081 ?hdi_val .
+      FILTER(xsd:double(?hdi_val) &gt; 0)
+    }
+    ORDER BY DESC(?hdi_val)
+    LIMIT 10
+  }
+  ?country rdfs:label ?countryLabel
+  FILTER(LANG(?countryLabel) = "en")
+  .
+  OPTIONAL {
+    ?country wdt:P2798 ?popGrowthRate .
+  }
+  OPTIONAL {
+    ?country p:P3864 ?maleStmt .
+    ?maleStmt ps:P3864 ?maleRate ; pq:P21 wd:Q6581072 .
+    FILTER(xsd:double(?maleRate) &gt; 0)
+  }
+  OPTIONAL {
+    ?country p:P3864 ?femaleStmt .
+    ?femaleStmt ps:P3864 ?femaleRate ; pq:P21 wd:Q6571072 .
+    FILTER(xsd:double(?femaleRate) &gt; 0)
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_time_complex/00061.json</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
       <c r="J81" s="7" t="inlineStr"/>
       <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
     </row>
     <row r="82" ht="65" customHeight="1">
       <c r="A82" s="4" t="n">
@@ -3477,19 +4493,29 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?eventLabel WHERE {
+  wd:Q3000357 rdfs:label ?eventLabel .
+  FILTER(LANG(?eventLabel) = "en")
+  FILTER(CONTAINS(?eventLabel , "Maldives"))
+}</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/OTT_QA_dev_complex/00147.json</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr"/>
-      <c r="H82" s="5" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr"/>
       <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="5" t="inlineStr"/>
     </row>
     <row r="83" ht="65" customHeight="1">
       <c r="A83" s="6" t="n">
@@ -3519,19 +4545,32 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?novel ?novelLabel ?city ?cityLabel WHERE {
+  ?novel wdt:P50 wd:Q5686 .
+  ?novel wdt:P840 ?city .
+  ?city wdt:P31 wd:Q515 .
+  ?novel rdfs:label ?novelLabel .
+  ?city rdfs:label ?cityLabel .
+  FILTER(LANG(?novelLabel) = 'en' &amp;&amp; LANG(?cityLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00054.json</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr"/>
       <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
     </row>
     <row r="84" ht="65" customHeight="1">
       <c r="A84" s="4" t="n">
@@ -3554,19 +4593,28 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q28132505 wdt:P577 ?date .
+  wd:Q28132505 wdt:P437 wd:Q6473564 .
+}</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00046.json</t>
         </is>
       </c>
-      <c r="G84" s="5" t="inlineStr"/>
-      <c r="H84" s="5" t="inlineStr"/>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr"/>
       <c r="K84" s="5" t="inlineStr"/>
+      <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="5" t="inlineStr"/>
     </row>
     <row r="85" ht="65" customHeight="1">
       <c r="A85" s="6" t="n">
@@ -3589,19 +4637,28 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
+          <t>SELECT(COUNT(?episode) AS ?episodeCount) WHERE {
+  ?season wdt:P179 wd:Q887734 ; wdt:P31 wd:Q2245476 ; wdt:P1545 "4" .
+  ?episode wdt:P31 wd:Q2119127 ; wdt:P53 ?season .
+}</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
           <t>Different answer</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00088.json</t>
         </is>
       </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
       <c r="J85" s="7" t="inlineStr"/>
       <c r="K85" s="7" t="inlineStr"/>
+      <c r="L85" s="7" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
     </row>
     <row r="86" ht="65" customHeight="1">
       <c r="A86" s="4" t="n">
@@ -3624,19 +4681,29 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?location ?locationLabel WHERE {
+  wd:Q37643 wdt:P276 ?location .
+  ?location rdfs:label ?locationLabel .
+  FILTER(LANG(?locationLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00353.json</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr"/>
-      <c r="H86" s="5" t="inlineStr"/>
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr"/>
       <c r="K86" s="5" t="inlineStr"/>
+      <c r="L86" s="5" t="inlineStr"/>
+      <c r="M86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="65" customHeight="1">
       <c r="A87" s="6" t="n">
@@ -3664,19 +4731,35 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?country ?countryLabel ?dish ?dishLabel WHERE {
+  wd:Q27231 wdt:P17 ?country .
+  ?country rdfs:label ?countryLabel .
+  FILTER(LANG(?countryLabel) = "en")
+  .
+  OPTIONAL {
+    ?country wdt:P8326 ?dish .
+    ?dish rdfs:label ?dishLabel .
+    FILTER(LANG(?dishLabel) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/Monaco_non_time_complex/00079.json</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
       <c r="I87" s="7" t="inlineStr"/>
       <c r="J87" s="7" t="inlineStr"/>
       <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88" ht="65" customHeight="1">
       <c r="A88" s="4" t="n">
@@ -3699,19 +4782,27 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?publicationDate WHERE {
+  wd:Q472208 wdt:P577 ?publicationDate .
+}</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F88" s="4" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00090.json</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr"/>
-      <c r="H88" s="5" t="inlineStr"/>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="5" t="inlineStr"/>
       <c r="K88" s="5" t="inlineStr"/>
+      <c r="L88" s="5" t="inlineStr"/>
+      <c r="M88" s="5" t="inlineStr"/>
     </row>
     <row r="89" ht="65" customHeight="1">
       <c r="A89" s="6" t="n">
@@ -3734,19 +4825,27 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?date WHERE {
+  wd:Q215410 wdt:P577 ?date .
+}</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_infobox_complex/00278.json</t>
         </is>
       </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
       <c r="I89" s="7" t="inlineStr"/>
       <c r="J89" s="7" t="inlineStr"/>
       <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90" ht="65" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -3776,19 +4875,34 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?event ?eventLabel ?date WHERE {
+  ?event rdfs:label ?eventLabel .
+  FILTER(LANG(?eventLabel) = "en")
+  .
+  FILTER(REGEX(?eventLabel , "memorial.*(wrestling|battle|show)|wrestling.*memorial" , "i"))
+  .
+  ?event wdt:P585 ?date .
+  FILTER(?date &gt;= "1980-01-01T00:00:00Z" ^^ xsd:dateTime)
+}
+ORDER BY ?date</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00035.json</t>
         </is>
       </c>
-      <c r="G90" s="5" t="inlineStr"/>
-      <c r="H90" s="5" t="inlineStr"/>
       <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="5" t="inlineStr"/>
       <c r="K90" s="5" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr"/>
+      <c r="M90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="65" customHeight="1">
       <c r="A91" s="6" t="n">
@@ -3811,19 +4925,27 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?end WHERE {
+  wd:Q41477806 wdt:P582 ?end
+}</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00514.json</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
       <c r="I91" s="7" t="inlineStr"/>
       <c r="J91" s="7" t="inlineStr"/>
       <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
     </row>
     <row r="92" ht="65" customHeight="1">
       <c r="A92" s="4" t="n">
@@ -3846,19 +4968,29 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?ruler WHERE {
+  wd:Q844536 wdt:P27 wd:Q11774 .
+  wd:Q844536 rdfs:label ?ruler .
+  FILTER(LANG(?ruler) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00775.json</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr"/>
-      <c r="H92" s="5" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="5" t="inlineStr"/>
       <c r="K92" s="5" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr"/>
+      <c r="M92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="65" customHeight="1">
       <c r="A93" s="6" t="n">
@@ -3881,19 +5013,29 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?location ?locationLabel WHERE {
+  wd:Q697407 wdt:P915 ?location .
+  ?location rdfs:label ?locationLabel .
+  FILTER(LANG(?locationLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/CompMix_table_simple_qa/00306.json</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
       <c r="I93" s="7" t="inlineStr"/>
       <c r="J93" s="7" t="inlineStr"/>
       <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
     </row>
     <row r="94" ht="65" customHeight="1">
       <c r="A94" s="4" t="n">
@@ -3920,19 +5062,37 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
+          <t>SELECT DISTINCT ?positionLabel WHERE {
+  ?position wdt:P31 / wdt:P279 * wd:Q1758037 .
+  ?person p:P39 ?positionStatement .
+  ?positionStatement ps:P39 ?position .
+  FILTER NOT EXISTS {
+    ?positionStatement pq:P582 ?endTime
+  }
+  .
+  ?position rdfs:label ?positionLabel .
+  FILTER(LANG(?positionLabel) = 'en')
+  .
+  FILTER(CONTAINS(LCASE(?positionLabel) , 'president'))
+}</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F94" s="4" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00018.json</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr"/>
-      <c r="H94" s="5" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="5" t="inlineStr"/>
       <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="65" customHeight="1">
       <c r="A95" s="6" t="n">
@@ -3955,19 +5115,29 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?lyricist ?lyricistLabel WHERE {
+  wd:Q127138 wdt:P676 ?lyricist .
+  ?lyricist rdfs:label ?lyricistLabel .
+  FILTER(LANG(?lyricistLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="H95" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00497.json</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr"/>
       <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
     </row>
     <row r="96" ht="65" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -3990,19 +5160,29 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?track ?trackLabel WHERE {
+  ?track wdt:P361 wd:Q27981679 .
+  ?track rdfs:label ?trackLabel .
+  FILTER(LANG(?trackLabel) = "en")
+}</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F96" s="4" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00558.json</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr"/>
-      <c r="H96" s="5" t="inlineStr"/>
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="5" t="inlineStr"/>
       <c r="K96" s="5" t="inlineStr"/>
+      <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="5" t="inlineStr"/>
     </row>
     <row r="97" ht="65" customHeight="1">
       <c r="A97" s="6" t="n">
@@ -4025,19 +5205,31 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?athlete ?name WHERE {
+  ?athlete wdt:P468 wd:Q2166602 .
+  OPTIONAL {
+    ?athlete rdfs:label ?name .
+    FILTER(LANG(?name) = "en")
+  }
+}</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>SimpleQA/Qampari_wikitables_simple/00054.json</t>
         </is>
       </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
       <c r="I97" s="7" t="inlineStr"/>
       <c r="J97" s="7" t="inlineStr"/>
       <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
     </row>
     <row r="98" ht="65" customHeight="1">
       <c r="A98" s="4" t="n">
@@ -4061,19 +5253,29 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
+          <t>SELECT ?genreLabel WHERE {
+  wd:Q30324921 wdt:P179 / wdt:P136 ?genre .
+  ?genre rdfs:label ?genreLabel .
+  FILTER(LANG(?genreLabel) = 'en')
+}</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
           <t>Higher accuracy in Table than in KG</t>
         </is>
       </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>SimpleQA/NQ_table_test_simple/00095.json</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr"/>
-      <c r="H98" s="5" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="5" t="inlineStr"/>
       <c r="K98" s="5" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr"/>
+      <c r="M98" s="5" t="inlineStr"/>
     </row>
     <row r="99" ht="65" customHeight="1">
       <c r="A99" s="6" t="n">
@@ -4096,27 +5298,37 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
+          <t>SELECT ?appearances WHERE {
+  wd:Q357984 p:P54 ?statement .
+  ?statement ps:P54 wd:Q166776 .
+  ?statement pq:P1350 ?appearances .
+}</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
           <t>Temporal changes</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>ComplexQA/CompMix_table_complex/00196.json</t>
         </is>
       </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="7" t="inlineStr"/>
       <c r="J99" s="7" t="inlineStr"/>
       <c r="K99" s="7" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K99"/>
+  <autoFilter ref="A1:M99"/>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Correct,Incorrect,Unsure"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H99 I2:I99 J2:J99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J99 K2:K99 L2:L99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
